--- a/Result/profitability/1459.xlsx
+++ b/Result/profitability/1459.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>-0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13625</v>
+        <v>0.2725</v>
       </c>
       <c r="N2" t="n">
-        <v>8.44125</v>
+        <v>12.4375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.45</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05625000000000001</v>
+        <v>0.20125</v>
       </c>
       <c r="N3" t="n">
-        <v>10.1425</v>
+        <v>13.43125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0425</v>
+        <v>0.29125</v>
       </c>
       <c r="N4" t="n">
-        <v>11.17875</v>
+        <v>13.755</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.06</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.001250000000000001</v>
+        <v>0.05500000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>7.031250000000001</v>
+        <v>8.192500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.52</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03999999999999999</v>
+        <v>0.06000000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>7.02</v>
+        <v>7.473750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.09125</v>
+        <v>0.04250000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>5.36</v>
+        <v>6.38875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.11375</v>
+        <v>0.04250000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>3.77875</v>
+        <v>4.3475</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1459</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>257</v>
+      </c>
+      <c r="D75" t="n">
+        <v>197</v>
+      </c>
+      <c r="E75" t="n">
+        <v>60</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="G75" t="n">
+        <v>23</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.10%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>395</v>
+      </c>
+      <c r="J75" t="n">
+        <v>419</v>
+      </c>
+      <c r="K75" t="n">
+        <v>385</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.35625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X75" t="n">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.550000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2409957627118644</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.4500000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5421686746987953</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.657001414427157</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
